--- a/test.xlsx
+++ b/test.xlsx
@@ -608,7 +608,7 @@
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
